--- a/data/nzd0102/nzd0102.xlsx
+++ b/data/nzd0102/nzd0102.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I338"/>
+  <dimension ref="A1:I340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11576,6 +11576,72 @@
         <v>340.03</v>
       </c>
       <c r="I338" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>362.97</v>
+      </c>
+      <c r="C339" t="n">
+        <v>348.14</v>
+      </c>
+      <c r="D339" t="n">
+        <v>344.3</v>
+      </c>
+      <c r="E339" t="n">
+        <v>346.2</v>
+      </c>
+      <c r="F339" t="n">
+        <v>346.18</v>
+      </c>
+      <c r="G339" t="n">
+        <v>348.34</v>
+      </c>
+      <c r="H339" t="n">
+        <v>339.84</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="C340" t="n">
+        <v>346.73</v>
+      </c>
+      <c r="D340" t="n">
+        <v>339.95</v>
+      </c>
+      <c r="E340" t="n">
+        <v>339.41</v>
+      </c>
+      <c r="F340" t="n">
+        <v>340.99</v>
+      </c>
+      <c r="G340" t="n">
+        <v>344.65</v>
+      </c>
+      <c r="H340" t="n">
+        <v>339.04</v>
+      </c>
+      <c r="I340" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11592,7 +11658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B364"/>
+  <dimension ref="A1:B366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15235,6 +15301,26 @@
       </c>
       <c r="B364" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -15403,28 +15489,28 @@
         <v>0.0764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2321356098365951</v>
+        <v>0.223386874456312</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04443386411924222</v>
+        <v>0.04160747246744267</v>
       </c>
       <c r="M2" t="n">
-        <v>6.386181799454692</v>
+        <v>6.391851134812566</v>
       </c>
       <c r="N2" t="n">
-        <v>64.57418131367028</v>
+        <v>64.51691178321893</v>
       </c>
       <c r="O2" t="n">
-        <v>8.035806201848716</v>
+        <v>8.032242014731562</v>
       </c>
       <c r="P2" t="n">
-        <v>364.1019735241513</v>
+        <v>364.1954988682018</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15481,28 +15567,28 @@
         <v>0.0772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2914691937755653</v>
+        <v>0.2756637155295589</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04580560235486464</v>
+        <v>0.04126709616462776</v>
       </c>
       <c r="M3" t="n">
-        <v>8.16146904142737</v>
+        <v>8.178286420853249</v>
       </c>
       <c r="N3" t="n">
-        <v>98.87797727370783</v>
+        <v>99.35582108712693</v>
       </c>
       <c r="O3" t="n">
-        <v>9.943740607724431</v>
+        <v>9.967739015801273</v>
       </c>
       <c r="P3" t="n">
-        <v>353.1171001932813</v>
+        <v>353.2859145100221</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15559,28 +15645,28 @@
         <v>0.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008356603652344337</v>
+        <v>-0.01610906325337184</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L4" t="n">
-        <v>2.923990340963911e-07</v>
+        <v>0.0001090611406929787</v>
       </c>
       <c r="M4" t="n">
-        <v>9.504320178352279</v>
+        <v>9.527650870257986</v>
       </c>
       <c r="N4" t="n">
-        <v>133.0819474290704</v>
+        <v>133.5373750723889</v>
       </c>
       <c r="O4" t="n">
-        <v>11.53611491920354</v>
+        <v>11.55583727266825</v>
       </c>
       <c r="P4" t="n">
-        <v>356.5713905000938</v>
+        <v>356.7527502231201</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15637,28 +15723,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2511209872760951</v>
+        <v>0.2332494368827274</v>
       </c>
       <c r="J5" t="n">
+        <v>339</v>
+      </c>
+      <c r="K5" t="n">
         <v>337</v>
       </c>
-      <c r="K5" t="n">
-        <v>335</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.02220117401164134</v>
+        <v>0.01928702107864788</v>
       </c>
       <c r="M5" t="n">
-        <v>9.964070891895974</v>
+        <v>9.98408488685123</v>
       </c>
       <c r="N5" t="n">
-        <v>155.1377606741007</v>
+        <v>155.641533578121</v>
       </c>
       <c r="O5" t="n">
-        <v>12.45543097103029</v>
+        <v>12.47563760206752</v>
       </c>
       <c r="P5" t="n">
-        <v>351.320675888707</v>
+        <v>351.5118448117645</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15715,28 +15801,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2347899577383267</v>
+        <v>0.2187614000841392</v>
       </c>
       <c r="J6" t="n">
+        <v>339</v>
+      </c>
+      <c r="K6" t="n">
         <v>337</v>
       </c>
-      <c r="K6" t="n">
-        <v>335</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03158351845571872</v>
+        <v>0.02756622190029767</v>
       </c>
       <c r="M6" t="n">
-        <v>7.687026973766263</v>
+        <v>7.703903269111462</v>
       </c>
       <c r="N6" t="n">
-        <v>93.77076230278185</v>
+        <v>94.33517876083218</v>
       </c>
       <c r="O6" t="n">
-        <v>9.683530466869087</v>
+        <v>9.712629858119385</v>
       </c>
       <c r="P6" t="n">
-        <v>350.9014191127462</v>
+        <v>351.073642140394</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15793,28 +15879,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1810628984051728</v>
+        <v>0.1664456939281371</v>
       </c>
       <c r="J7" t="n">
+        <v>339</v>
+      </c>
+      <c r="K7" t="n">
         <v>337</v>
       </c>
-      <c r="K7" t="n">
-        <v>335</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.02170363963573618</v>
+        <v>0.01843834677573164</v>
       </c>
       <c r="M7" t="n">
-        <v>7.074809655183643</v>
+        <v>7.085219618579233</v>
       </c>
       <c r="N7" t="n">
-        <v>81.97917678156773</v>
+        <v>82.4119581281786</v>
       </c>
       <c r="O7" t="n">
-        <v>9.054235295239888</v>
+        <v>9.078103223040516</v>
       </c>
       <c r="P7" t="n">
-        <v>354.0573491002256</v>
+        <v>354.2144044292631</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15871,28 +15957,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0475538634085247</v>
+        <v>0.03188898365855369</v>
       </c>
       <c r="J8" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K8" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001065047486464965</v>
+        <v>0.0004813362174090896</v>
       </c>
       <c r="M8" t="n">
-        <v>8.512175548605223</v>
+        <v>8.528936554716012</v>
       </c>
       <c r="N8" t="n">
-        <v>117.6677837987734</v>
+        <v>118.0042426173096</v>
       </c>
       <c r="O8" t="n">
-        <v>10.84747822301448</v>
+        <v>10.86297577173537</v>
       </c>
       <c r="P8" t="n">
-        <v>351.4957304836711</v>
+        <v>351.6638379050481</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -15930,7 +16016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I338"/>
+  <dimension ref="A1:I340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31783,6 +31869,100 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-35.83572683609441,174.5728024561128</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-35.83638001838195,174.57323644538906</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-35.83697609167181,174.57377053764648</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-35.837496944152235,174.57441914417478</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-35.837964557204465,174.57512866000206</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-35.83837719768777,174.57588619170983</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-35.83875601427874,174.57667677038643</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-35.835728089841425,174.57280056925322</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-35.836388053784134,174.5732243522619</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-35.83700224717903,174.57373466235543</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-35.8375424140394,174.57436882985155</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-35.83800205525401,174.57509430648471</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-35.838406154878555,174.5758660941247</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-35.83876259786115,174.57667315692396</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0102/nzd0102.xlsx
+++ b/data/nzd0102/nzd0102.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I340"/>
+  <dimension ref="A1:I342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,72 @@
       <c r="I340" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>363.17</v>
+      </c>
+      <c r="C341" t="n">
+        <v>347.56</v>
+      </c>
+      <c r="D341" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="E341" t="n">
+        <v>338.48</v>
+      </c>
+      <c r="F341" t="n">
+        <v>341.45</v>
+      </c>
+      <c r="G341" t="n">
+        <v>345.5</v>
+      </c>
+      <c r="H341" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>364.7</v>
+      </c>
+      <c r="C342" t="n">
+        <v>348.37</v>
+      </c>
+      <c r="D342" t="n">
+        <v>341.49</v>
+      </c>
+      <c r="E342" t="n">
+        <v>339.54</v>
+      </c>
+      <c r="F342" t="n">
+        <v>342.53</v>
+      </c>
+      <c r="G342" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="H342" t="n">
+        <v>341.11</v>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15321,6 +15387,26 @@
       </c>
       <c r="B366" t="n">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>-0.16</v>
       </c>
     </row>
   </sheetData>
@@ -15489,28 +15575,28 @@
         <v>0.0764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.223386874456312</v>
+        <v>0.2161260283774012</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04160747246744267</v>
+        <v>0.03940803424984096</v>
       </c>
       <c r="M2" t="n">
-        <v>6.391851134812566</v>
+        <v>6.390180488883525</v>
       </c>
       <c r="N2" t="n">
-        <v>64.51691178321893</v>
+        <v>64.36865425292791</v>
       </c>
       <c r="O2" t="n">
-        <v>8.032242014731562</v>
+        <v>8.023007805862331</v>
       </c>
       <c r="P2" t="n">
-        <v>364.1954988682018</v>
+        <v>364.2733907154959</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15567,28 +15653,28 @@
         <v>0.0772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2756637155295589</v>
+        <v>0.260913790107184</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04126709616462776</v>
+        <v>0.03725705787740097</v>
       </c>
       <c r="M3" t="n">
-        <v>8.178286420853249</v>
+        <v>8.19183490542531</v>
       </c>
       <c r="N3" t="n">
-        <v>99.35582108712693</v>
+        <v>99.71101706551845</v>
       </c>
       <c r="O3" t="n">
-        <v>9.967739015801273</v>
+        <v>9.985540399273264</v>
       </c>
       <c r="P3" t="n">
-        <v>353.2859145100221</v>
+        <v>353.4440271692617</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15645,28 +15731,28 @@
         <v>0.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01610906325337184</v>
+        <v>-0.0339043699825616</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001090611406929787</v>
+        <v>0.0004842899798369604</v>
       </c>
       <c r="M4" t="n">
-        <v>9.527650870257986</v>
+        <v>9.555228983356532</v>
       </c>
       <c r="N4" t="n">
-        <v>133.5373750723889</v>
+        <v>134.1163952153429</v>
       </c>
       <c r="O4" t="n">
-        <v>11.55583727266825</v>
+        <v>11.58086331908562</v>
       </c>
       <c r="P4" t="n">
-        <v>356.7527502231201</v>
+        <v>356.9438945612345</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15723,28 +15809,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2332494368827274</v>
+        <v>0.2114925135629928</v>
       </c>
       <c r="J5" t="n">
+        <v>341</v>
+      </c>
+      <c r="K5" t="n">
         <v>339</v>
       </c>
-      <c r="K5" t="n">
-        <v>337</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01928702107864788</v>
+        <v>0.0159097791725854</v>
       </c>
       <c r="M5" t="n">
-        <v>9.98408488685123</v>
+        <v>10.02260839331155</v>
       </c>
       <c r="N5" t="n">
-        <v>155.641533578121</v>
+        <v>156.7691674086642</v>
       </c>
       <c r="O5" t="n">
-        <v>12.47563760206752</v>
+        <v>12.52074947471852</v>
       </c>
       <c r="P5" t="n">
-        <v>351.5118448117645</v>
+        <v>351.7454053264408</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15801,28 +15887,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2187614000841392</v>
+        <v>0.2013398595619058</v>
       </c>
       <c r="J6" t="n">
+        <v>341</v>
+      </c>
+      <c r="K6" t="n">
         <v>339</v>
       </c>
-      <c r="K6" t="n">
-        <v>337</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02756622190029767</v>
+        <v>0.02343315470682938</v>
       </c>
       <c r="M6" t="n">
-        <v>7.703903269111462</v>
+        <v>7.725424699558214</v>
       </c>
       <c r="N6" t="n">
-        <v>94.33517876083218</v>
+        <v>95.07923212475258</v>
       </c>
       <c r="O6" t="n">
-        <v>9.712629858119385</v>
+        <v>9.750858019925866</v>
       </c>
       <c r="P6" t="n">
-        <v>351.073642140394</v>
+        <v>351.2614965835378</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15879,28 +15965,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1664456939281371</v>
+        <v>0.1517323635953641</v>
       </c>
       <c r="J7" t="n">
+        <v>341</v>
+      </c>
+      <c r="K7" t="n">
         <v>339</v>
       </c>
-      <c r="K7" t="n">
-        <v>337</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01843834677573164</v>
+        <v>0.01539780124012191</v>
       </c>
       <c r="M7" t="n">
-        <v>7.085219618579233</v>
+        <v>7.096421361277392</v>
       </c>
       <c r="N7" t="n">
-        <v>82.4119581281786</v>
+        <v>82.85399713898521</v>
       </c>
       <c r="O7" t="n">
-        <v>9.078103223040516</v>
+        <v>9.102417104208376</v>
       </c>
       <c r="P7" t="n">
-        <v>354.2144044292631</v>
+        <v>354.3730549599866</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15957,28 +16043,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03188898365855369</v>
+        <v>0.01812434769353404</v>
       </c>
       <c r="J8" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K8" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004813362174090896</v>
+        <v>0.0001565024069680732</v>
       </c>
       <c r="M8" t="n">
-        <v>8.528936554716012</v>
+        <v>8.537707784453866</v>
       </c>
       <c r="N8" t="n">
-        <v>118.0042426173096</v>
+        <v>118.1213291724255</v>
       </c>
       <c r="O8" t="n">
-        <v>10.86297577173537</v>
+        <v>10.86836368421785</v>
       </c>
       <c r="P8" t="n">
-        <v>351.6638379050481</v>
+        <v>351.812086310833</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16016,7 +16102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I340"/>
+  <dimension ref="A1:I342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31963,6 +32049,100 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-35.83572569632436,174.57280417143966</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-35.836383323724824,174.5732314709115</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-35.83699948130978,174.57373845606548</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-35.83754864187217,174.57436193848912</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-35.83799873172782,174.57509735130643</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-35.83839948452322,174.57587072365098</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-35.8387527224875,174.57667857711743</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-35.83571697708275,174.57281729368842</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-35.83637870764247,174.57323841802656</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-35.836992987529364,174.5737473630359</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-35.83754154348211,174.5743697931602</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-35.83799092866609,174.5751045000173</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-35.83839085229844,174.57587671480152</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-35.83874556284145,174.57668250675687</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0102/nzd0102.xlsx
+++ b/data/nzd0102/nzd0102.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I342"/>
+  <dimension ref="A1:I343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11710,6 +11710,39 @@
       <c r="I342" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>363.82</v>
+      </c>
+      <c r="C343" t="n">
+        <v>348.06</v>
+      </c>
+      <c r="D343" t="n">
+        <v>341.09</v>
+      </c>
+      <c r="E343" t="n">
+        <v>337.83</v>
+      </c>
+      <c r="F343" t="n">
+        <v>341.26</v>
+      </c>
+      <c r="G343" t="n">
+        <v>345.26</v>
+      </c>
+      <c r="H343" t="n">
+        <v>340.68</v>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15407,6 +15440,16 @@
       </c>
       <c r="B368" t="n">
         <v>-0.16</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -15575,28 +15618,28 @@
         <v>0.0764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2161260283774012</v>
+        <v>0.2124821134369231</v>
       </c>
       <c r="J2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03940803424984096</v>
+        <v>0.03831474683894509</v>
       </c>
       <c r="M2" t="n">
-        <v>6.390180488883525</v>
+        <v>6.389824372551023</v>
       </c>
       <c r="N2" t="n">
-        <v>64.36865425292791</v>
+        <v>64.2954969945951</v>
       </c>
       <c r="O2" t="n">
-        <v>8.023007805862331</v>
+        <v>8.018447293247933</v>
       </c>
       <c r="P2" t="n">
-        <v>364.2733907154959</v>
+        <v>364.312649737987</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15653,28 +15696,28 @@
         <v>0.0772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.260913790107184</v>
+        <v>0.2537222587185544</v>
       </c>
       <c r="J3" t="n">
+        <v>342</v>
+      </c>
+      <c r="K3" t="n">
         <v>341</v>
       </c>
-      <c r="K3" t="n">
-        <v>340</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.03725705787740097</v>
+        <v>0.03537144855747409</v>
       </c>
       <c r="M3" t="n">
-        <v>8.19183490542531</v>
+        <v>8.198460688140463</v>
       </c>
       <c r="N3" t="n">
-        <v>99.71101706551845</v>
+        <v>99.86835846075692</v>
       </c>
       <c r="O3" t="n">
-        <v>9.985540399273264</v>
+        <v>9.993415755424014</v>
       </c>
       <c r="P3" t="n">
-        <v>353.4440271692617</v>
+        <v>353.521441095521</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15731,28 +15774,28 @@
         <v>0.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0339043699825616</v>
+        <v>-0.04254946262538796</v>
       </c>
       <c r="J4" t="n">
+        <v>342</v>
+      </c>
+      <c r="K4" t="n">
         <v>341</v>
       </c>
-      <c r="K4" t="n">
-        <v>340</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0004842899798369604</v>
+        <v>0.0007638223527951515</v>
       </c>
       <c r="M4" t="n">
-        <v>9.555228983356532</v>
+        <v>9.568100794514173</v>
       </c>
       <c r="N4" t="n">
-        <v>134.1163952153429</v>
+        <v>134.3712946177122</v>
       </c>
       <c r="O4" t="n">
-        <v>11.58086331908562</v>
+        <v>11.59186329360868</v>
       </c>
       <c r="P4" t="n">
-        <v>356.9438945612345</v>
+        <v>357.0371438354886</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15809,28 +15852,28 @@
         <v>0.0641</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2114925135629928</v>
+        <v>0.2001309210933811</v>
       </c>
       <c r="J5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0159097791725854</v>
+        <v>0.01426091619714109</v>
       </c>
       <c r="M5" t="n">
-        <v>10.02260839331155</v>
+        <v>10.0457243111341</v>
       </c>
       <c r="N5" t="n">
-        <v>156.7691674086642</v>
+        <v>157.4315887765334</v>
       </c>
       <c r="O5" t="n">
-        <v>12.52074947471852</v>
+        <v>12.54717453359653</v>
       </c>
       <c r="P5" t="n">
-        <v>351.7454053264408</v>
+        <v>351.8678853062695</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15887,28 +15930,28 @@
         <v>0.0611</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2013398595619058</v>
+        <v>0.1923638776463611</v>
       </c>
       <c r="J6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02343315470682938</v>
+        <v>0.02141788815588419</v>
       </c>
       <c r="M6" t="n">
-        <v>7.725424699558214</v>
+        <v>7.737124508718112</v>
       </c>
       <c r="N6" t="n">
-        <v>95.07923212475258</v>
+        <v>95.49447016034871</v>
       </c>
       <c r="O6" t="n">
-        <v>9.750858019925866</v>
+        <v>9.772127207540265</v>
       </c>
       <c r="P6" t="n">
-        <v>351.2614965835378</v>
+        <v>351.3586892074263</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15965,28 +16008,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1517323635953641</v>
+        <v>0.1440497513835031</v>
       </c>
       <c r="J7" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K7" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01539780124012191</v>
+        <v>0.01390440408954141</v>
       </c>
       <c r="M7" t="n">
-        <v>7.096421361277392</v>
+        <v>7.102884605703498</v>
       </c>
       <c r="N7" t="n">
-        <v>82.85399713898521</v>
+        <v>83.11936480722908</v>
       </c>
       <c r="O7" t="n">
-        <v>9.102417104208376</v>
+        <v>9.116982220407643</v>
       </c>
       <c r="P7" t="n">
-        <v>354.3730549599866</v>
+        <v>354.456242877054</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16043,28 +16086,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01812434769353404</v>
+        <v>0.01137748352547325</v>
       </c>
       <c r="J8" t="n">
+        <v>342</v>
+      </c>
+      <c r="K8" t="n">
         <v>341</v>
       </c>
-      <c r="K8" t="n">
-        <v>340</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0001565024069680732</v>
+        <v>6.187615908004318e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>8.537707784453866</v>
+        <v>8.541711293006282</v>
       </c>
       <c r="N8" t="n">
-        <v>118.1213291724255</v>
+        <v>118.1671895056257</v>
       </c>
       <c r="O8" t="n">
-        <v>10.86836368421785</v>
+        <v>10.87047328802319</v>
       </c>
       <c r="P8" t="n">
-        <v>351.812086310833</v>
+        <v>351.8850554768331</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -16102,7 +16145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I342"/>
+  <dimension ref="A1:I343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32143,6 +32186,53 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-35.83572199207156,174.57280974625158</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-35.83638047429131,174.57323575925423</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-35.83699539263329,174.57374406415812</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-35.837552994658296,174.57435712194487</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-35.83800010448865,174.5750960936627</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-35.838401367917676,174.57586941649072</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-35.8387491015171,174.57668056452135</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
